--- a/cari acik/odemeler_dengesi_tablo.xlsx
+++ b/cari acik/odemeler_dengesi_tablo.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,42 +429,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Kalem</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>_level</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Aylık (Cari)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Aylık (Önceki Yıl)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>İlk 6 Ay (Cari)</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>İlk 6 Ay (Önceki Yıl)</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>İlk 7 Ay (Cari)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>İlk 7 Ay (Önceki Yıl)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>12 Aylık (Cari)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>12 Aylık (Önceki Yıl)</t>
         </is>
@@ -468,22 +480,22 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-4194</v>
+        <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>-2270</v>
+        <v>1762</v>
       </c>
       <c r="E2" t="n">
-        <v>-34548</v>
+        <v>-34830</v>
       </c>
       <c r="F2" t="n">
-        <v>-25998</v>
+        <v>-24254</v>
       </c>
       <c r="G2" t="n">
-        <v>-38888</v>
+        <v>-40706</v>
       </c>
       <c r="H2" t="n">
-        <v>-24198</v>
+        <v>-23985</v>
       </c>
     </row>
     <row r="3">
@@ -496,22 +508,22 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>-8533</v>
+        <v>-5579</v>
       </c>
       <c r="D3" t="n">
-        <v>-6521</v>
+        <v>-4561</v>
       </c>
       <c r="E3" t="n">
-        <v>-43720</v>
+        <v>-49365</v>
       </c>
       <c r="F3" t="n">
-        <v>-37063</v>
+        <v>-41342</v>
       </c>
       <c r="G3" t="n">
-        <v>-76515</v>
+        <v>-77166</v>
       </c>
       <c r="H3" t="n">
-        <v>-63097</v>
+        <v>-62313</v>
       </c>
     </row>
     <row r="4">
@@ -524,22 +536,22 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>24429</v>
+        <v>25185</v>
       </c>
       <c r="D4" t="n">
-        <v>20334</v>
+        <v>24620</v>
       </c>
       <c r="E4" t="n">
-        <v>133125</v>
+        <v>158245</v>
       </c>
       <c r="F4" t="n">
-        <v>131012</v>
+        <v>155619</v>
       </c>
       <c r="G4" t="n">
-        <v>272786</v>
+        <v>273266</v>
       </c>
       <c r="H4" t="n">
-        <v>264877</v>
+        <v>267523</v>
       </c>
     </row>
     <row r="5">
@@ -552,22 +564,22 @@
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>192</v>
+        <v>484</v>
       </c>
       <c r="D5" t="n">
-        <v>128</v>
+        <v>442</v>
       </c>
       <c r="E5" t="n">
-        <v>1574</v>
+        <v>2058</v>
       </c>
       <c r="F5" t="n">
-        <v>1770</v>
+        <v>2212</v>
       </c>
       <c r="G5" t="n">
-        <v>2858</v>
+        <v>2900</v>
       </c>
       <c r="H5" t="n">
-        <v>4031</v>
+        <v>3742</v>
       </c>
     </row>
     <row r="6">
@@ -580,22 +592,22 @@
         <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>24237</v>
+        <v>24701</v>
       </c>
       <c r="D6" t="n">
-        <v>20206</v>
+        <v>24178</v>
       </c>
       <c r="E6" t="n">
-        <v>131551</v>
+        <v>156187</v>
       </c>
       <c r="F6" t="n">
-        <v>129242</v>
+        <v>153407</v>
       </c>
       <c r="G6" t="n">
-        <v>269928</v>
+        <v>270366</v>
       </c>
       <c r="H6" t="n">
-        <v>260846</v>
+        <v>263781</v>
       </c>
     </row>
     <row r="7">
@@ -608,22 +620,22 @@
         <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>32962</v>
+        <v>30764</v>
       </c>
       <c r="D7" t="n">
-        <v>26855</v>
+        <v>29181</v>
       </c>
       <c r="E7" t="n">
-        <v>176845</v>
+        <v>207610</v>
       </c>
       <c r="F7" t="n">
-        <v>168075</v>
+        <v>196961</v>
       </c>
       <c r="G7" t="n">
-        <v>349301</v>
+        <v>350432</v>
       </c>
       <c r="H7" t="n">
-        <v>327974</v>
+        <v>329836</v>
       </c>
     </row>
     <row r="8">
@@ -636,22 +648,22 @@
         <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>1352</v>
+        <v>946</v>
       </c>
       <c r="D8" t="n">
-        <v>1551</v>
+        <v>943</v>
       </c>
       <c r="E8" t="n">
-        <v>9041</v>
+        <v>9987</v>
       </c>
       <c r="F8" t="n">
-        <v>11241</v>
+        <v>12184</v>
       </c>
       <c r="G8" t="n">
-        <v>20929</v>
+        <v>20932</v>
       </c>
       <c r="H8" t="n">
-        <v>20557</v>
+        <v>20502</v>
       </c>
     </row>
     <row r="9">
@@ -664,22 +676,22 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>6851</v>
+        <v>8228</v>
       </c>
       <c r="D9" t="n">
-        <v>6088</v>
+        <v>8015</v>
       </c>
       <c r="E9" t="n">
-        <v>23807</v>
+        <v>31797</v>
       </c>
       <c r="F9" t="n">
-        <v>23563</v>
+        <v>31278</v>
       </c>
       <c r="G9" t="n">
-        <v>63747</v>
+        <v>63515</v>
       </c>
       <c r="H9" t="n">
-        <v>61564</v>
+        <v>61309</v>
       </c>
     </row>
     <row r="10">
@@ -692,22 +704,22 @@
         <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>12169</v>
+        <v>13325</v>
       </c>
       <c r="D10" t="n">
-        <v>11350</v>
+        <v>13162</v>
       </c>
       <c r="E10" t="n">
-        <v>52648</v>
+        <v>65943</v>
       </c>
       <c r="F10" t="n">
-        <v>51915</v>
+        <v>66085</v>
       </c>
       <c r="G10" t="n">
-        <v>123337</v>
+        <v>124738</v>
       </c>
       <c r="H10" t="n">
-        <v>119091</v>
+        <v>120864</v>
       </c>
     </row>
     <row r="11">
@@ -720,22 +732,22 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>4246</v>
+        <v>4585</v>
       </c>
       <c r="D11" t="n">
-        <v>3669</v>
+        <v>4145</v>
       </c>
       <c r="E11" t="n">
-        <v>19905</v>
+        <v>24435</v>
       </c>
       <c r="F11" t="n">
-        <v>19106</v>
+        <v>23353</v>
       </c>
       <c r="G11" t="n">
-        <v>43247</v>
+        <v>43651</v>
       </c>
       <c r="H11" t="n">
-        <v>41099</v>
+        <v>41482</v>
       </c>
     </row>
     <row r="12">
@@ -748,22 +760,22 @@
         <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>5799</v>
+        <v>6964</v>
       </c>
       <c r="D12" t="n">
-        <v>5953</v>
+        <v>7021</v>
       </c>
       <c r="E12" t="n">
-        <v>24037</v>
+        <v>31001</v>
       </c>
       <c r="F12" t="n">
-        <v>23767</v>
+        <v>30788</v>
       </c>
       <c r="G12" t="n">
-        <v>60265</v>
+        <v>60251</v>
       </c>
       <c r="H12" t="n">
-        <v>58017</v>
+        <v>58155</v>
       </c>
     </row>
     <row r="13">
@@ -776,22 +788,22 @@
         <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>2124</v>
+        <v>1776</v>
       </c>
       <c r="D13" t="n">
-        <v>1728</v>
+        <v>1996</v>
       </c>
       <c r="E13" t="n">
-        <v>8706</v>
+        <v>10507</v>
       </c>
       <c r="F13" t="n">
-        <v>9042</v>
+        <v>11944</v>
       </c>
       <c r="G13" t="n">
-        <v>19825</v>
+        <v>20836</v>
       </c>
       <c r="H13" t="n">
-        <v>19975</v>
+        <v>21227</v>
       </c>
     </row>
     <row r="14">
@@ -804,22 +816,22 @@
         <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>5318</v>
+        <v>5097</v>
       </c>
       <c r="D14" t="n">
-        <v>5262</v>
+        <v>5147</v>
       </c>
       <c r="E14" t="n">
-        <v>28841</v>
+        <v>34146</v>
       </c>
       <c r="F14" t="n">
-        <v>28352</v>
+        <v>34807</v>
       </c>
       <c r="G14" t="n">
-        <v>59590</v>
+        <v>61223</v>
       </c>
       <c r="H14" t="n">
-        <v>57527</v>
+        <v>59555</v>
       </c>
     </row>
     <row r="15">
@@ -832,22 +844,22 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>1649</v>
+        <v>1692</v>
       </c>
       <c r="D15" t="n">
-        <v>1633</v>
+        <v>1736</v>
       </c>
       <c r="E15" t="n">
-        <v>9071</v>
+        <v>10762</v>
       </c>
       <c r="F15" t="n">
-        <v>9537</v>
+        <v>11420</v>
       </c>
       <c r="G15" t="n">
-        <v>19112</v>
+        <v>19119</v>
       </c>
       <c r="H15" t="n">
-        <v>20383</v>
+        <v>20400</v>
       </c>
     </row>
     <row r="16">
@@ -860,22 +872,22 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>942</v>
+        <v>996</v>
       </c>
       <c r="D16" t="n">
-        <v>938</v>
+        <v>819</v>
       </c>
       <c r="E16" t="n">
-        <v>4873</v>
+        <v>5869</v>
       </c>
       <c r="F16" t="n">
-        <v>4919</v>
+        <v>5738</v>
       </c>
       <c r="G16" t="n">
-        <v>8921</v>
+        <v>9098</v>
       </c>
       <c r="H16" t="n">
-        <v>8762</v>
+        <v>8916</v>
       </c>
     </row>
     <row r="17">
@@ -888,22 +900,22 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>2727</v>
+        <v>2409</v>
       </c>
       <c r="D17" t="n">
-        <v>2691</v>
+        <v>2592</v>
       </c>
       <c r="E17" t="n">
-        <v>14897</v>
+        <v>17515</v>
       </c>
       <c r="F17" t="n">
-        <v>13896</v>
+        <v>17649</v>
       </c>
       <c r="G17" t="n">
-        <v>31557</v>
+        <v>33006</v>
       </c>
       <c r="H17" t="n">
-        <v>28382</v>
+        <v>30239</v>
       </c>
     </row>
     <row r="18">
@@ -916,22 +928,22 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>-2512</v>
+        <v>-2613</v>
       </c>
       <c r="D18" t="n">
-        <v>-1837</v>
+        <v>-1692</v>
       </c>
       <c r="E18" t="n">
-        <v>-14635</v>
+        <v>-17262</v>
       </c>
       <c r="F18" t="n">
-        <v>-12498</v>
+        <v>-14190</v>
       </c>
       <c r="G18" t="n">
-        <v>-26120</v>
+        <v>-27055</v>
       </c>
       <c r="H18" t="n">
-        <v>-22665</v>
+        <v>-22981</v>
       </c>
     </row>
     <row r="19">
@@ -944,22 +956,22 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>-3034</v>
+        <v>498</v>
       </c>
       <c r="D19" t="n">
-        <v>-847</v>
+        <v>2263</v>
       </c>
       <c r="E19" t="n">
-        <v>-27081</v>
+        <v>-26901</v>
       </c>
       <c r="F19" t="n">
-        <v>-16527</v>
+        <v>-14282</v>
       </c>
       <c r="G19" t="n">
-        <v>-20817</v>
+        <v>-22674</v>
       </c>
       <c r="H19" t="n">
-        <v>-7672</v>
+        <v>-7225</v>
       </c>
     </row>
   </sheetData>

--- a/cari acik/odemeler_dengesi_tablo.xlsx
+++ b/cari acik/odemeler_dengesi_tablo.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,42 +417,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Kalem</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>_level</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Aylık (Cari)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Aylık (Önceki Yıl)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>İlk 7 Ay (Cari)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>İlk 7 Ay (Önceki Yıl)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>12 Aylık (Cari)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>12 Aylık (Önceki Yıl)</t>
         </is>

--- a/cari acik/odemeler_dengesi_tablo.xlsx
+++ b/cari acik/odemeler_dengesi_tablo.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,42 +429,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Kalem</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>_level</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Aylık (Cari)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Aylık (Önceki Yıl)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>İlk 7 Ay (Cari)</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>İlk 7 Ay (Önceki Yıl)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>12 Aylık (Cari)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>12 Aylık (Önceki Yıl)</t>
         </is>

--- a/cari acik/odemeler_dengesi_tablo.xlsx
+++ b/cari acik/odemeler_dengesi_tablo.xlsx
@@ -439,12 +439,12 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>İlk 7 Ay (Cari)</t>
+          <t>İlk 8 Ay (Cari)</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>İlk 7 Ay (Önceki Yıl)</t>
+          <t>İlk 8 Ay (Önceki Yıl)</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -468,22 +468,22 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>36</v>
+        <v>4053</v>
       </c>
       <c r="D2" t="n">
-        <v>1762</v>
+        <v>4622</v>
       </c>
       <c r="E2" t="n">
-        <v>-34830</v>
+        <v>-31498</v>
       </c>
       <c r="F2" t="n">
-        <v>-24254</v>
+        <v>-19671</v>
       </c>
       <c r="G2" t="n">
-        <v>-40706</v>
+        <v>-42103</v>
       </c>
       <c r="H2" t="n">
-        <v>-23985</v>
+        <v>-23828</v>
       </c>
     </row>
     <row r="3">
@@ -496,22 +496,22 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>-5579</v>
+        <v>-3746</v>
       </c>
       <c r="D3" t="n">
-        <v>-4561</v>
+        <v>-2800</v>
       </c>
       <c r="E3" t="n">
-        <v>-49365</v>
+        <v>-53338</v>
       </c>
       <c r="F3" t="n">
-        <v>-41342</v>
+        <v>-44196</v>
       </c>
       <c r="G3" t="n">
-        <v>-77166</v>
+        <v>-78448</v>
       </c>
       <c r="H3" t="n">
-        <v>-62313</v>
+        <v>-62281</v>
       </c>
     </row>
     <row r="4">
@@ -524,22 +524,22 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>25185</v>
+        <v>23327</v>
       </c>
       <c r="D4" t="n">
-        <v>24620</v>
+        <v>21409</v>
       </c>
       <c r="E4" t="n">
-        <v>158245</v>
+        <v>181563</v>
       </c>
       <c r="F4" t="n">
-        <v>155619</v>
+        <v>177028</v>
       </c>
       <c r="G4" t="n">
-        <v>273266</v>
+        <v>275175</v>
       </c>
       <c r="H4" t="n">
-        <v>267523</v>
+        <v>267210</v>
       </c>
     </row>
     <row r="5">
@@ -552,22 +552,22 @@
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>484</v>
+        <v>1149</v>
       </c>
       <c r="D5" t="n">
-        <v>442</v>
+        <v>159</v>
       </c>
       <c r="E5" t="n">
-        <v>2058</v>
+        <v>3207</v>
       </c>
       <c r="F5" t="n">
-        <v>2212</v>
+        <v>2371</v>
       </c>
       <c r="G5" t="n">
-        <v>2900</v>
+        <v>3890</v>
       </c>
       <c r="H5" t="n">
-        <v>3742</v>
+        <v>3358</v>
       </c>
     </row>
     <row r="6">
@@ -580,22 +580,22 @@
         <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>24701</v>
+        <v>22178</v>
       </c>
       <c r="D6" t="n">
-        <v>24178</v>
+        <v>21250</v>
       </c>
       <c r="E6" t="n">
-        <v>156187</v>
+        <v>178356</v>
       </c>
       <c r="F6" t="n">
-        <v>153407</v>
+        <v>174657</v>
       </c>
       <c r="G6" t="n">
-        <v>270366</v>
+        <v>271285</v>
       </c>
       <c r="H6" t="n">
-        <v>263781</v>
+        <v>263852</v>
       </c>
     </row>
     <row r="7">
@@ -608,22 +608,22 @@
         <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>30764</v>
+        <v>27073</v>
       </c>
       <c r="D7" t="n">
-        <v>29181</v>
+        <v>24209</v>
       </c>
       <c r="E7" t="n">
-        <v>207610</v>
+        <v>234901</v>
       </c>
       <c r="F7" t="n">
-        <v>196961</v>
+        <v>221224</v>
       </c>
       <c r="G7" t="n">
-        <v>350432</v>
+        <v>353623</v>
       </c>
       <c r="H7" t="n">
-        <v>329836</v>
+        <v>329491</v>
       </c>
     </row>
     <row r="8">
@@ -636,22 +636,22 @@
         <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>946</v>
+        <v>323</v>
       </c>
       <c r="D8" t="n">
-        <v>943</v>
+        <v>1146</v>
       </c>
       <c r="E8" t="n">
-        <v>9987</v>
+        <v>10310</v>
       </c>
       <c r="F8" t="n">
-        <v>12184</v>
+        <v>13330</v>
       </c>
       <c r="G8" t="n">
-        <v>20932</v>
+        <v>20109</v>
       </c>
       <c r="H8" t="n">
-        <v>20502</v>
+        <v>20355</v>
       </c>
     </row>
     <row r="9">
@@ -664,22 +664,22 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>8228</v>
+        <v>9711</v>
       </c>
       <c r="D9" t="n">
-        <v>8015</v>
+        <v>9343</v>
       </c>
       <c r="E9" t="n">
-        <v>31797</v>
+        <v>41502</v>
       </c>
       <c r="F9" t="n">
-        <v>31278</v>
+        <v>40625</v>
       </c>
       <c r="G9" t="n">
-        <v>63515</v>
+        <v>63872</v>
       </c>
       <c r="H9" t="n">
-        <v>61309</v>
+        <v>61438</v>
       </c>
     </row>
     <row r="10">
@@ -692,22 +692,22 @@
         <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>13325</v>
+        <v>14658</v>
       </c>
       <c r="D10" t="n">
-        <v>13162</v>
+        <v>14314</v>
       </c>
       <c r="E10" t="n">
-        <v>65943</v>
+        <v>80601</v>
       </c>
       <c r="F10" t="n">
-        <v>66085</v>
+        <v>80410</v>
       </c>
       <c r="G10" t="n">
-        <v>124738</v>
+        <v>125074</v>
       </c>
       <c r="H10" t="n">
-        <v>120864</v>
+        <v>121511</v>
       </c>
     </row>
     <row r="11">
@@ -720,22 +720,22 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>4585</v>
+        <v>4952</v>
       </c>
       <c r="D11" t="n">
-        <v>4145</v>
+        <v>4274</v>
       </c>
       <c r="E11" t="n">
-        <v>24435</v>
+        <v>29387</v>
       </c>
       <c r="F11" t="n">
-        <v>23353</v>
+        <v>27638</v>
       </c>
       <c r="G11" t="n">
-        <v>43651</v>
+        <v>44321</v>
       </c>
       <c r="H11" t="n">
-        <v>41482</v>
+        <v>41670</v>
       </c>
     </row>
     <row r="12">
@@ -748,22 +748,22 @@
         <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>6964</v>
+        <v>8197</v>
       </c>
       <c r="D12" t="n">
-        <v>7021</v>
+        <v>8378</v>
       </c>
       <c r="E12" t="n">
-        <v>31001</v>
+        <v>39198</v>
       </c>
       <c r="F12" t="n">
-        <v>30788</v>
+        <v>39166</v>
       </c>
       <c r="G12" t="n">
-        <v>60251</v>
+        <v>60070</v>
       </c>
       <c r="H12" t="n">
-        <v>58155</v>
+        <v>58370</v>
       </c>
     </row>
     <row r="13">
@@ -776,22 +776,22 @@
         <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>1776</v>
+        <v>1509</v>
       </c>
       <c r="D13" t="n">
-        <v>1996</v>
+        <v>1662</v>
       </c>
       <c r="E13" t="n">
-        <v>10507</v>
+        <v>12016</v>
       </c>
       <c r="F13" t="n">
-        <v>11944</v>
+        <v>13606</v>
       </c>
       <c r="G13" t="n">
-        <v>20836</v>
+        <v>20683</v>
       </c>
       <c r="H13" t="n">
-        <v>21227</v>
+        <v>21471</v>
       </c>
     </row>
     <row r="14">
@@ -804,22 +804,22 @@
         <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>5097</v>
+        <v>4947</v>
       </c>
       <c r="D14" t="n">
-        <v>5147</v>
+        <v>4971</v>
       </c>
       <c r="E14" t="n">
-        <v>34146</v>
+        <v>39099</v>
       </c>
       <c r="F14" t="n">
-        <v>34807</v>
+        <v>39785</v>
       </c>
       <c r="G14" t="n">
-        <v>61223</v>
+        <v>61202</v>
       </c>
       <c r="H14" t="n">
-        <v>59555</v>
+        <v>60073</v>
       </c>
     </row>
     <row r="15">
@@ -832,22 +832,22 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>1692</v>
+        <v>1687</v>
       </c>
       <c r="D15" t="n">
-        <v>1736</v>
+        <v>1529</v>
       </c>
       <c r="E15" t="n">
-        <v>10762</v>
+        <v>12449</v>
       </c>
       <c r="F15" t="n">
-        <v>11420</v>
+        <v>12956</v>
       </c>
       <c r="G15" t="n">
-        <v>19119</v>
+        <v>19274</v>
       </c>
       <c r="H15" t="n">
-        <v>20400</v>
+        <v>20158</v>
       </c>
     </row>
     <row r="16">
@@ -860,22 +860,22 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>996</v>
+        <v>912</v>
       </c>
       <c r="D16" t="n">
-        <v>819</v>
+        <v>755</v>
       </c>
       <c r="E16" t="n">
-        <v>5869</v>
+        <v>6781</v>
       </c>
       <c r="F16" t="n">
-        <v>5738</v>
+        <v>6493</v>
       </c>
       <c r="G16" t="n">
-        <v>9098</v>
+        <v>9255</v>
       </c>
       <c r="H16" t="n">
-        <v>8916</v>
+        <v>9059</v>
       </c>
     </row>
     <row r="17">
@@ -888,22 +888,22 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>2409</v>
+        <v>2348</v>
       </c>
       <c r="D17" t="n">
-        <v>2592</v>
+        <v>2687</v>
       </c>
       <c r="E17" t="n">
-        <v>17515</v>
+        <v>19869</v>
       </c>
       <c r="F17" t="n">
-        <v>17649</v>
+        <v>20336</v>
       </c>
       <c r="G17" t="n">
-        <v>33006</v>
+        <v>32673</v>
       </c>
       <c r="H17" t="n">
-        <v>30239</v>
+        <v>30856</v>
       </c>
     </row>
     <row r="18">
@@ -916,22 +916,22 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>-2613</v>
+        <v>-1912</v>
       </c>
       <c r="D18" t="n">
-        <v>-1692</v>
+        <v>-1921</v>
       </c>
       <c r="E18" t="n">
-        <v>-17262</v>
+        <v>-19662</v>
       </c>
       <c r="F18" t="n">
-        <v>-14190</v>
+        <v>-16100</v>
       </c>
       <c r="G18" t="n">
-        <v>-27055</v>
+        <v>-27527</v>
       </c>
       <c r="H18" t="n">
-        <v>-22981</v>
+        <v>-22985</v>
       </c>
     </row>
     <row r="19">
@@ -944,22 +944,22 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>498</v>
+        <v>3227</v>
       </c>
       <c r="D19" t="n">
-        <v>2263</v>
+        <v>5609</v>
       </c>
       <c r="E19" t="n">
-        <v>-26901</v>
+        <v>-24395</v>
       </c>
       <c r="F19" t="n">
-        <v>-14282</v>
+        <v>-8712</v>
       </c>
       <c r="G19" t="n">
-        <v>-22674</v>
+        <v>-25884</v>
       </c>
       <c r="H19" t="n">
-        <v>-7225</v>
+        <v>-6831</v>
       </c>
     </row>
   </sheetData>

--- a/cari acik/odemeler_dengesi_tablo.xlsx
+++ b/cari acik/odemeler_dengesi_tablo.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,42 +429,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Kalem</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>_level</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Aylık (Cari)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Aylık (Önceki Yıl)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>İlk 8 Ay (Cari)</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>İlk 8 Ay (Önceki Yıl)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>12 Aylık (Cari)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>12 Aylık (Önceki Yıl)</t>
         </is>

--- a/cari acik/odemeler_dengesi_tablo.xlsx
+++ b/cari acik/odemeler_dengesi_tablo.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,42 +417,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Kalem</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>_level</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Aylık (Cari)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Aylık (Önceki Yıl)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>İlk 8 Ay (Cari)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>İlk 8 Ay (Önceki Yıl)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>12 Aylık (Cari)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>12 Aylık (Önceki Yıl)</t>
         </is>
